--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending5(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending5(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_结局5（上）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="448">
   <si>
     <t>ID</t>
   </si>
@@ -258,6 +258,12 @@
     <t>撒谎！</t>
   </si>
   <si>
+    <t>10 enhanced suspense</t>
+  </si>
+  <si>
+    <t>charfadeout(L,1)&amp;unlockmusic(Music10)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_You; 层级=17</t>
   </si>
   <si>
@@ -342,15 +348,6 @@
     <t>源类型=type:txt_pb; 层级=27</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>盖曼脸上的温和瞬间僵住，他抬起头看向你，原本平稳的呼吸终于出现了一丝不易察觉的慌乱。但他还是竭力克制住这些情绪，试图解释什么。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Gaiman; 层级=28</t>
-  </si>
-  <si>
     <t>31</t>
   </si>
   <si>
@@ -378,12 +375,6 @@
     <t>源类型=type:txt_pb; 层级=31</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=32</t>
-  </si>
-  <si>
     <t>35</t>
   </si>
   <si>
@@ -558,6 +549,12 @@
     <t>那张疲惫的、温和的、一直试图表达某种深沉理解的面孔，在此刻像是被人从内部撤走了一根支撑的柱子。他盖曼的肩膀微微垮了一下，嘴角的弧度消失了，眼里的光泽收拢成两粒极小的、冰冷的点。</t>
   </si>
   <si>
+    <t>3 enhanced leberch-horror-night</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music3)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=51</t>
   </si>
   <si>
@@ -706,6 +703,12 @@
   </si>
   <si>
     <t>这一次，盖曼沉默了格外长的时间。房间里只剩下培养罐里液体缓慢流动的细微声响，和你们三个人各自的呼吸声。直到一声坚定的否决声从他口中跳了出来，那是带着某种决心的承诺，快到令人猝不及防。</t>
+  </si>
+  <si>
+    <t>13 enhanced_audioatlant-total-war-epic-action-cinematic-trailer-main</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music13)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=67</t>
@@ -897,6 +900,9 @@
   </si>
   <si>
     <t>命令库行数</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>说话人映射数</t>
@@ -2596,7 +2602,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3319,21 +3325,21 @@
         <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="L19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3351,7 +3357,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3366,12 +3372,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
         <v>29</v>
@@ -3389,7 +3395,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3404,12 +3410,12 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" ht="42" spans="1:12">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
@@ -3427,7 +3433,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3442,12 +3448,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>29</v>
@@ -3465,7 +3471,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3480,12 +3486,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" ht="55.5" spans="1:12">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3503,7 +3509,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3518,12 +3524,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" ht="69" spans="1:12">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3541,7 +3547,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3556,12 +3562,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" ht="40.5" spans="1:12">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3579,7 +3585,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3594,12 +3600,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" ht="57" spans="1:12">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
         <v>29</v>
@@ -3617,7 +3623,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3632,12 +3638,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3655,7 +3661,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3670,22 +3676,19 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" ht="40.5" spans="1:12">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" ht="42" spans="1:12">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
-      <c r="D29" t="s">
-        <v>40</v>
-      </c>
       <c r="E29" t="s">
         <v>15</v>
       </c>
@@ -3693,7 +3696,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3704,25 +3707,22 @@
       <c r="J29" t="s">
         <v>15</v>
       </c>
-      <c r="K29" t="s">
-        <v>42</v>
-      </c>
       <c r="L29" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" ht="42" spans="1:12">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" ht="57" spans="1:12">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3731,7 +3731,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3743,15 +3743,15 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" ht="57" spans="1:12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" ht="54" spans="1:12">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3769,7 +3769,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3784,21 +3784,21 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" ht="54" spans="1:12">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" ht="28.5" spans="1:12">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -3807,7 +3807,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3819,15 +3819,15 @@
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="L32" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" ht="54" spans="1:12">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" ht="40.5" spans="1:12">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3836,7 +3836,7 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -3845,7 +3845,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3860,22 +3860,22 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" ht="67.5" spans="1:12">
+      <c r="A34" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="34" ht="28.5" spans="1:12">
-      <c r="A34" t="s">
-        <v>116</v>
-      </c>
-      <c r="B34" t="s">
-        <v>117</v>
-      </c>
-      <c r="C34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" t="s">
-        <v>118</v>
-      </c>
       <c r="E34" t="s">
         <v>15</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3895,15 +3895,15 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" ht="40.5" spans="1:12">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3912,7 +3912,7 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -3921,7 +3921,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3933,24 +3933,24 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="L35" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" ht="67.5" spans="1:12">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" ht="40.5" spans="1:12">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -3959,7 +3959,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3974,21 +3974,21 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" ht="40.5" spans="1:12">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" ht="54" spans="1:12">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -3997,7 +3997,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4009,15 +4009,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="38" ht="40.5" spans="1:12">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" ht="42" spans="1:12">
       <c r="A38" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4035,7 +4035,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4050,21 +4050,21 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="39" ht="54" spans="1:12">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4073,7 +4073,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4085,15 +4085,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="L39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" ht="42" spans="1:12">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" ht="27" spans="1:12">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4102,7 +4102,7 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4111,7 +4111,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4126,21 +4126,21 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" ht="28.5" spans="1:12">
       <c r="A41" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4149,7 +4149,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4161,15 +4161,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="42" ht="27" spans="1:12">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" ht="40.5" spans="1:12">
       <c r="A42" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4178,7 +4178,7 @@
         <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4187,7 +4187,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4202,21 +4202,21 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="43" ht="28.5" spans="1:12">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" ht="57" spans="1:12">
       <c r="A43" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4225,7 +4225,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4240,135 +4240,135 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="44" ht="40.5" spans="1:12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" ht="57" spans="1:12">
       <c r="A44" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" t="s">
+        <v>115</v>
+      </c>
+      <c r="E44" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s">
+        <v>152</v>
+      </c>
+      <c r="H44" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" t="s">
+        <v>15</v>
+      </c>
+      <c r="J44" t="s">
+        <v>15</v>
+      </c>
+      <c r="K44" t="s">
+        <v>15</v>
+      </c>
+      <c r="L44" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" ht="42" spans="1:12">
+      <c r="A45" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" t="s">
+        <v>115</v>
+      </c>
+      <c r="E45" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s">
+        <v>155</v>
+      </c>
+      <c r="H45" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" t="s">
+        <v>15</v>
+      </c>
+      <c r="J45" t="s">
+        <v>15</v>
+      </c>
+      <c r="K45" t="s">
+        <v>15</v>
+      </c>
+      <c r="L45" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s">
+        <v>158</v>
+      </c>
+      <c r="H46" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" t="s">
+        <v>15</v>
+      </c>
+      <c r="J46" t="s">
+        <v>15</v>
+      </c>
+      <c r="K46" t="s">
+        <v>46</v>
+      </c>
+      <c r="L46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="47" ht="27" spans="1:12">
+      <c r="A47" t="s">
+        <v>160</v>
+      </c>
+      <c r="B47" t="s">
         <v>13</v>
       </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" t="s">
-        <v>118</v>
-      </c>
-      <c r="E44" t="s">
-        <v>15</v>
-      </c>
-      <c r="F44" t="s">
-        <v>15</v>
-      </c>
-      <c r="G44" t="s">
-        <v>149</v>
-      </c>
-      <c r="H44" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" t="s">
-        <v>15</v>
-      </c>
-      <c r="J44" t="s">
-        <v>15</v>
-      </c>
-      <c r="K44" t="s">
-        <v>15</v>
-      </c>
-      <c r="L44" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="45" ht="57" spans="1:12">
-      <c r="A45" t="s">
-        <v>151</v>
-      </c>
-      <c r="B45" t="s">
-        <v>117</v>
-      </c>
-      <c r="C45" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" t="s">
-        <v>118</v>
-      </c>
-      <c r="E45" t="s">
-        <v>15</v>
-      </c>
-      <c r="F45" t="s">
-        <v>15</v>
-      </c>
-      <c r="G45" t="s">
-        <v>152</v>
-      </c>
-      <c r="H45" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" t="s">
-        <v>15</v>
-      </c>
-      <c r="J45" t="s">
-        <v>15</v>
-      </c>
-      <c r="K45" t="s">
-        <v>15</v>
-      </c>
-      <c r="L45" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" ht="57" spans="1:12">
-      <c r="A46" t="s">
-        <v>154</v>
-      </c>
-      <c r="B46" t="s">
-        <v>117</v>
-      </c>
-      <c r="C46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" t="s">
-        <v>118</v>
-      </c>
-      <c r="E46" t="s">
-        <v>15</v>
-      </c>
-      <c r="F46" t="s">
-        <v>15</v>
-      </c>
-      <c r="G46" t="s">
-        <v>155</v>
-      </c>
-      <c r="H46" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" t="s">
-        <v>15</v>
-      </c>
-      <c r="J46" t="s">
-        <v>15</v>
-      </c>
-      <c r="K46" t="s">
-        <v>15</v>
-      </c>
-      <c r="L46" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="47" ht="42" spans="1:12">
-      <c r="A47" t="s">
-        <v>157</v>
-      </c>
-      <c r="B47" t="s">
-        <v>117</v>
-      </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4377,7 +4377,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4392,12 +4392,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="48" ht="43.5" spans="1:12">
       <c r="A48" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B48" t="s">
         <v>29</v>
@@ -4406,7 +4406,7 @@
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4415,7 +4415,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4427,57 +4427,57 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49" ht="27" spans="1:12">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" ht="55.5" spans="1:12">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B49" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s">
+        <v>167</v>
+      </c>
+      <c r="H49" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" t="s">
+        <v>15</v>
+      </c>
+      <c r="J49" t="s">
+        <v>15</v>
+      </c>
+      <c r="K49" t="s">
+        <v>15</v>
+      </c>
+      <c r="L49" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" ht="54" spans="1:12">
+      <c r="A50" t="s">
+        <v>169</v>
+      </c>
+      <c r="B50" t="s">
         <v>13</v>
       </c>
-      <c r="C49" t="s">
-        <v>14</v>
-      </c>
-      <c r="D49" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" t="s">
-        <v>164</v>
-      </c>
-      <c r="H49" t="s">
-        <v>15</v>
-      </c>
-      <c r="I49" t="s">
-        <v>15</v>
-      </c>
-      <c r="J49" t="s">
-        <v>15</v>
-      </c>
-      <c r="K49" t="s">
-        <v>15</v>
-      </c>
-      <c r="L49" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="50" ht="43.5" spans="1:12">
-      <c r="A50" t="s">
-        <v>166</v>
-      </c>
-      <c r="B50" t="s">
-        <v>29</v>
-      </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
@@ -4491,36 +4491,36 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
       </c>
       <c r="I50" t="s">
-        <v>15</v>
+        <v>171</v>
       </c>
       <c r="J50" t="s">
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="L50" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="51" ht="55.5" spans="1:12">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" ht="30" spans="1:12">
       <c r="A51" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4529,7 +4529,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4541,15 +4541,15 @@
         <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="L51" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="52" ht="54" spans="1:12">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="52" ht="30" spans="1:12">
       <c r="A52" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4558,7 +4558,7 @@
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4567,7 +4567,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4582,12 +4582,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="53" ht="30" spans="1:12">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="53" ht="54" spans="1:12">
       <c r="A53" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B53" t="s">
         <v>39</v>
@@ -4605,7 +4605,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4617,15 +4617,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="54" ht="30" spans="1:12">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="54" ht="40.5" spans="1:12">
       <c r="A54" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4643,7 +4643,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4655,24 +4655,24 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="L54" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="55" ht="54" spans="1:12">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="55" ht="55.5" spans="1:12">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B55" t="s">
-        <v>39</v>
+        <v>187</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>40</v>
+        <v>188</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4681,7 +4681,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4693,15 +4693,15 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="L55" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="56" ht="40.5" spans="1:12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="56" ht="27" spans="1:12">
       <c r="A56" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4710,7 +4710,7 @@
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>40</v>
+        <v>188</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -4719,7 +4719,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4734,21 +4734,21 @@
         <v>46</v>
       </c>
       <c r="L56" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="57" ht="55.5" spans="1:12">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" ht="69" spans="1:12">
       <c r="A57" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>189</v>
+        <v>15</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4757,7 +4757,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4769,15 +4769,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="58" ht="27" spans="1:12">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="58" ht="40.5" spans="1:12">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4786,7 +4786,7 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>189</v>
+        <v>15</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4795,7 +4795,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4807,18 +4807,18 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>46</v>
+        <v>199</v>
       </c>
       <c r="L58" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="59" ht="69" spans="1:12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" ht="40.5" spans="1:12">
       <c r="A59" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
@@ -4833,7 +4833,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4848,12 +4848,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="60" ht="40.5" spans="1:12">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="60" ht="28.5" spans="1:12">
       <c r="A60" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4871,7 +4871,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4883,18 +4883,18 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="61" ht="40.5" spans="1:12">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B61" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -4909,7 +4909,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4924,12 +4924,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="62" ht="28.5" spans="1:12">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4947,7 +4947,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -4962,12 +4962,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="63" ht="40.5" spans="1:12">
       <c r="A63" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B63" t="s">
         <v>39</v>
@@ -4985,7 +4985,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5000,15 +5000,15 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="64" ht="40.5" spans="1:12">
       <c r="A64" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -5023,7 +5023,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5038,92 +5038,92 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" ht="40.5" spans="1:12">
       <c r="A65" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B65" t="s">
+        <v>114</v>
+      </c>
+      <c r="C65" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65" t="s">
+        <v>219</v>
+      </c>
+      <c r="H65" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J65" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" t="s">
+        <v>15</v>
+      </c>
+      <c r="L65" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="66" ht="75" spans="1:12">
+      <c r="A66" t="s">
+        <v>221</v>
+      </c>
+      <c r="B66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s">
+        <v>222</v>
+      </c>
+      <c r="H66" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" t="s">
+        <v>223</v>
+      </c>
+      <c r="J66" t="s">
+        <v>15</v>
+      </c>
+      <c r="K66" t="s">
+        <v>224</v>
+      </c>
+      <c r="L66" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="67" ht="28.5" spans="1:12">
+      <c r="A67" t="s">
+        <v>226</v>
+      </c>
+      <c r="B67" t="s">
         <v>39</v>
       </c>
-      <c r="C65" t="s">
-        <v>14</v>
-      </c>
-      <c r="D65" t="s">
-        <v>15</v>
-      </c>
-      <c r="E65" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" t="s">
-        <v>15</v>
-      </c>
-      <c r="G65" t="s">
-        <v>215</v>
-      </c>
-      <c r="H65" t="s">
-        <v>15</v>
-      </c>
-      <c r="I65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J65" t="s">
-        <v>15</v>
-      </c>
-      <c r="K65" t="s">
-        <v>15</v>
-      </c>
-      <c r="L65" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="66" ht="40.5" spans="1:12">
-      <c r="A66" t="s">
-        <v>217</v>
-      </c>
-      <c r="B66" t="s">
-        <v>39</v>
-      </c>
-      <c r="C66" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" t="s">
-        <v>15</v>
-      </c>
-      <c r="G66" t="s">
-        <v>215</v>
-      </c>
-      <c r="H66" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" t="s">
-        <v>15</v>
-      </c>
-      <c r="J66" t="s">
-        <v>15</v>
-      </c>
-      <c r="K66" t="s">
-        <v>15</v>
-      </c>
-      <c r="L66" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="67" ht="40.5" spans="1:12">
-      <c r="A67" t="s">
-        <v>219</v>
-      </c>
-      <c r="B67" t="s">
-        <v>117</v>
-      </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5152,12 +5152,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="68" ht="67.5" spans="1:12">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="68" ht="55.5" spans="1:12">
       <c r="A68" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5175,7 +5175,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5190,15 +5190,15 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="69" ht="28.5" spans="1:12">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B69" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -5213,7 +5213,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5225,15 +5225,15 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>15</v>
+        <v>234</v>
       </c>
       <c r="L69" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="70" ht="55.5" spans="1:12">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="70" ht="27" spans="1:12">
       <c r="A70" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5251,7 +5251,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5263,15 +5263,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="L70" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" ht="40.5" spans="1:12">
       <c r="A71" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5289,7 +5289,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5301,15 +5301,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="72" ht="27" spans="1:12">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5327,7 +5327,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5339,15 +5339,15 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>237</v>
+        <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="73" ht="40.5" spans="1:12">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="73" ht="42" spans="1:12">
       <c r="A73" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5365,7 +5365,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5380,15 +5380,15 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="74" ht="40.5" spans="1:12">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -5403,7 +5403,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5418,12 +5418,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="75" ht="42" spans="1:12">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="75" ht="40.5" spans="1:12">
       <c r="A75" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5441,7 +5441,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5456,12 +5456,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B76" t="s">
         <v>29</v>
@@ -5479,7 +5479,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5494,12 +5494,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="77" ht="40.5" spans="1:12">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="77" ht="54" spans="1:12">
       <c r="A77" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5517,7 +5517,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5532,15 +5532,15 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="78" ht="67.5" spans="1:12">
       <c r="A78" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B78" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -5555,7 +5555,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5567,15 +5567,15 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>15</v>
+        <v>263</v>
       </c>
       <c r="L78" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79" ht="54" spans="1:12">
       <c r="A79" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5593,7 +5593,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5604,87 +5604,11 @@
       <c r="J79" t="s">
         <v>15</v>
       </c>
-      <c r="K79" t="s">
-        <v>15</v>
+      <c r="K79" s="2" t="s">
+        <v>267</v>
       </c>
       <c r="L79" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="80" ht="67.5" spans="1:12">
-      <c r="A80" t="s">
-        <v>260</v>
-      </c>
-      <c r="B80" t="s">
-        <v>13</v>
-      </c>
-      <c r="C80" t="s">
-        <v>14</v>
-      </c>
-      <c r="D80" t="s">
-        <v>15</v>
-      </c>
-      <c r="E80" t="s">
-        <v>15</v>
-      </c>
-      <c r="F80" t="s">
-        <v>15</v>
-      </c>
-      <c r="G80" t="s">
-        <v>261</v>
-      </c>
-      <c r="H80" t="s">
-        <v>15</v>
-      </c>
-      <c r="I80" t="s">
-        <v>15</v>
-      </c>
-      <c r="J80" t="s">
-        <v>15</v>
-      </c>
-      <c r="K80" t="s">
-        <v>262</v>
-      </c>
-      <c r="L80" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="81" ht="54" spans="1:12">
-      <c r="A81" t="s">
-        <v>264</v>
-      </c>
-      <c r="B81" t="s">
-        <v>13</v>
-      </c>
-      <c r="C81" t="s">
-        <v>14</v>
-      </c>
-      <c r="D81" t="s">
-        <v>15</v>
-      </c>
-      <c r="E81" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" t="s">
-        <v>15</v>
-      </c>
-      <c r="G81" t="s">
-        <v>265</v>
-      </c>
-      <c r="H81" t="s">
-        <v>15</v>
-      </c>
-      <c r="I81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J81" t="s">
-        <v>15</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="L81" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -5705,47 +5629,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -5753,7 +5677,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5761,66 +5685,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -5842,616 +5766,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C13" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D13" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F13" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B14" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F14" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B16" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C16" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D16" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E16" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F16" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B17" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C17" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D17" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E17" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B18" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C18" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D18" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E18" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F18" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B19" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C19" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D19" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E19" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F19" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B20" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C20" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D20" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E20" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F20" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B21" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C21" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D21" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E21" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F21" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B22" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C22" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D22" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E22" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F22" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B23" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C23" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D23" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E23" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F23" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B24" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C24" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D24" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E24" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F24" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B25" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C25" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D25" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E25" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F25" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B26" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C26" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D26" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E26" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F26" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B27" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C27" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D27" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E27" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F27" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B28" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C28" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D28" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E28" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F28" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B29" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C29" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D29" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E29" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F29" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B30" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C30" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D30" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E30" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F30" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B31" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C31" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D31" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
